--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K110"/>
+  <dimension ref="A1:K111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4075,9 +4075,6 @@
           <t>비케이홀딩스(23,534,735주)</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260903000395</t>
@@ -4111,10 +4108,6 @@
       <c r="F108" t="n">
         <v>20000001094</v>
       </c>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260903000316</t>
@@ -4148,10 +4141,6 @@
       <c r="F109" t="n">
         <v>20000000000</v>
       </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260903000285</t>
@@ -4185,13 +4174,46 @@
       <c r="F110" t="n">
         <v>2299998987</v>
       </c>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260903000148</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>20260907</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>파인디앤씨</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>6000001375</v>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260907000075</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K111"/>
+  <dimension ref="A1:K112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4207,13 +4207,46 @@
       <c r="F111" t="n">
         <v>6000001375</v>
       </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260907000075</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>더코디</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>30000000000</v>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260908000001</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K112"/>
+  <dimension ref="A1:K116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4240,13 +4240,157 @@
       <c r="F112" t="n">
         <v>30000000000</v>
       </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260908000001</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>20260909</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>바른손이앤에이</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>2629998460</v>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260909000531</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>20260909</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>SKAI</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>1999998990</v>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260909000507</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>20260909</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>아리바이오LAB</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260909000478</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>20260909</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>넥사다이내믹스</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>29999998875</v>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260909000002</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K116"/>
+  <dimension ref="A1:K126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4273,10 +4273,6 @@
       <c r="F113" t="n">
         <v>2629998460</v>
       </c>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260909000531</t>
@@ -4310,10 +4306,6 @@
       <c r="F114" t="n">
         <v>1999998990</v>
       </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260909000507</t>
@@ -4347,10 +4339,6 @@
       <c r="F115" t="n">
         <v>7000000000</v>
       </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260909000478</t>
@@ -4384,13 +4372,379 @@
       <c r="F116" t="n">
         <v>29999998875</v>
       </c>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260909000002</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>우성머티리얼스</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>1999997860</v>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260910000580</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>CSA 코스믹</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>18000000000</v>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260910000549</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>크라우드웍스</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>999999781</v>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260910000465</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>헝셩그룹</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>60000000000</v>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260910000423</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>넥써쓰</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>3797296895</v>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260910000357</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>E8</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>2999999560</v>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260910000322</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>GMI벤처</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>2499997350</v>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260910000314</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>바이오비쥬</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>60000000000</v>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260910000280</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>아이엘</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>7800000000</v>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260910000248</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>엠젠솔루션</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>4999999297</v>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260909000543</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K126"/>
+  <dimension ref="A1:K134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4405,10 +4405,6 @@
       <c r="F117" t="n">
         <v>1999997860</v>
       </c>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260910000580</t>
@@ -4442,10 +4438,6 @@
       <c r="F118" t="n">
         <v>18000000000</v>
       </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260910000549</t>
@@ -4479,10 +4471,6 @@
       <c r="F119" t="n">
         <v>999999781</v>
       </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260910000465</t>
@@ -4516,10 +4504,6 @@
       <c r="F120" t="n">
         <v>60000000000</v>
       </c>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260910000423</t>
@@ -4553,10 +4537,6 @@
       <c r="F121" t="n">
         <v>3797296895</v>
       </c>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260910000357</t>
@@ -4590,10 +4570,6 @@
       <c r="F122" t="n">
         <v>2999999560</v>
       </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260910000322</t>
@@ -4627,10 +4603,6 @@
       <c r="F123" t="n">
         <v>2499997350</v>
       </c>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260910000314</t>
@@ -4664,10 +4636,6 @@
       <c r="F124" t="n">
         <v>60000000000</v>
       </c>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260910000280</t>
@@ -4701,10 +4669,6 @@
       <c r="F125" t="n">
         <v>7800000000</v>
       </c>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260910000248</t>
@@ -4738,13 +4702,309 @@
       <c r="F126" t="n">
         <v>4999999297</v>
       </c>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260909000543</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>멕아이씨에스</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>990000000</v>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260914000397</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>HLB글로벌</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>5000000000</v>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260914000322</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>아리바이오LAB</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260914000312</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>이브이첨단소재</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>2999994240</v>
+      </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260914000246</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>링크솔루션</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>30000000000</v>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260914000252</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>이브이첨단소재</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>5499996600</v>
+      </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260914000244</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>이노테나</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>5000000000</v>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260914000062</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>KS인더스트리</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>7000000000</v>
+      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260911000607</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K134"/>
+  <dimension ref="A1:K139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4735,10 +4735,6 @@
       <c r="F127" t="n">
         <v>990000000</v>
       </c>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260914000397</t>
@@ -4772,10 +4768,6 @@
       <c r="F128" t="n">
         <v>5000000000</v>
       </c>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260914000322</t>
@@ -4809,10 +4801,6 @@
       <c r="F129" t="n">
         <v>3000000000</v>
       </c>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260914000312</t>
@@ -4846,10 +4834,6 @@
       <c r="F130" t="n">
         <v>2999994240</v>
       </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260914000246</t>
@@ -4883,10 +4867,6 @@
       <c r="F131" t="n">
         <v>30000000000</v>
       </c>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260914000252</t>
@@ -4920,10 +4900,6 @@
       <c r="F132" t="n">
         <v>5499996600</v>
       </c>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260914000244</t>
@@ -4957,14 +4933,11 @@
       <c r="F133" t="n">
         <v>5000000000</v>
       </c>
-      <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260914000062</t>
@@ -4998,13 +4971,202 @@
       <c r="F134" t="n">
         <v>7000000000</v>
       </c>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260911000607</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>비케이홀딩스</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>4734000000</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>비케이홀딩스(30,534,735주)</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260915000428</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>화일약품</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260915000382</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>화일약품</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>9999993120</v>
+      </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260915000380</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>광진실업</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>1999996960</v>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260915000331</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>미투온</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>27900249356</v>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260915000295</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K139"/>
+  <dimension ref="A1:K145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5009,9 +5009,6 @@
           <t>비케이홀딩스(30,534,735주)</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260915000428</t>
@@ -5045,14 +5042,11 @@
       <c r="F136" t="n">
         <v>10000000000</v>
       </c>
-      <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260915000382</t>
@@ -5086,10 +5080,6 @@
       <c r="F137" t="n">
         <v>9999993120</v>
       </c>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260915000380</t>
@@ -5123,10 +5113,6 @@
       <c r="F138" t="n">
         <v>1999996960</v>
       </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260915000331</t>
@@ -5160,13 +5146,228 @@
       <c r="F139" t="n">
         <v>27900249356</v>
       </c>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260915000295</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>앤씨앤</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260916000548</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>STX</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>68000000000</v>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260916000543</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>STX</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260916000537</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>GMI벤처</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>489997955</v>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260916000465</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>삼진식품</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>BW</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260916000348</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>모아라이프플러스</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260916000279</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K145"/>
+  <dimension ref="A1:K149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5179,10 +5179,6 @@
       <c r="F140" t="n">
         <v>10000000000</v>
       </c>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260916000548</t>
@@ -5216,10 +5212,6 @@
       <c r="F141" t="n">
         <v>68000000000</v>
       </c>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260916000543</t>
@@ -5250,10 +5242,6 @@
           <t>유상증자(보통주식)</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260916000537</t>
@@ -5287,10 +5275,6 @@
       <c r="F143" t="n">
         <v>489997955</v>
       </c>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260916000465</t>
@@ -5324,10 +5308,6 @@
       <c r="F144" t="n">
         <v>10000000000</v>
       </c>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260916000348</t>
@@ -5361,13 +5341,157 @@
       <c r="F145" t="n">
         <v>2000000000</v>
       </c>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260916000279</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>시선AI</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>5000000000</v>
+      </c>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260921000413</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>특수건설</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260921000401</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>아틀라스링크</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>13500000000</v>
+      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260921000354</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>파인디앤씨</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>13000000000</v>
+      </c>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260921000198</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K149"/>
+  <dimension ref="A1:K154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5374,10 +5374,6 @@
       <c r="F146" t="n">
         <v>5000000000</v>
       </c>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260921000413</t>
@@ -5411,10 +5407,6 @@
       <c r="F147" t="n">
         <v>10000000000</v>
       </c>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260921000401</t>
@@ -5448,10 +5440,6 @@
       <c r="F148" t="n">
         <v>13500000000</v>
       </c>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260921000354</t>
@@ -5485,13 +5473,194 @@
       <c r="F149" t="n">
         <v>13000000000</v>
       </c>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260921000198</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>셀리드</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>2999997000</v>
+      </c>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260922000533</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>에이전트AI</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>12000000000</v>
+      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260922000374</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>엑스플러스</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>14000000000</v>
+      </c>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260922000356</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>코람코라이프인프라리츠</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260921000428</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>코람코라이프인프라리츠</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>24000000000</v>
+      </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260921000425</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K154"/>
+  <dimension ref="A1:K157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5506,10 +5506,6 @@
       <c r="F150" t="n">
         <v>2999997000</v>
       </c>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260922000533</t>
@@ -5543,10 +5539,6 @@
       <c r="F151" t="n">
         <v>12000000000</v>
       </c>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260922000374</t>
@@ -5580,10 +5572,6 @@
       <c r="F152" t="n">
         <v>14000000000</v>
       </c>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260922000356</t>
@@ -5617,10 +5605,6 @@
       <c r="F153" t="n">
         <v>10000000000</v>
       </c>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260921000428</t>
@@ -5654,13 +5638,120 @@
       <c r="F154" t="n">
         <v>24000000000</v>
       </c>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260921000425</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>케이쓰리아이</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>2998993060</v>
+      </c>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260923000638</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>케이쓰리아이</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>15000000000</v>
+      </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260923000637</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>휴림로봇</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>2000008360</v>
+      </c>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260923000576</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K157"/>
+  <dimension ref="A1:K158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5671,10 +5671,6 @@
       <c r="F155" t="n">
         <v>2998993060</v>
       </c>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260923000638</t>
@@ -5708,10 +5704,6 @@
       <c r="F156" t="n">
         <v>15000000000</v>
       </c>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260923000637</t>
@@ -5745,13 +5737,46 @@
       <c r="F157" t="n">
         <v>2000008360</v>
       </c>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260923000576</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>20260928</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>크라우드웍스</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>1924887972</v>
+      </c>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260928000378</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K158"/>
+  <dimension ref="A1:K160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5770,13 +5770,83 @@
       <c r="F158" t="n">
         <v>1924887972</v>
       </c>
-      <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260928000378</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>리튬포어스</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>1100002810</v>
+      </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260929000646</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>MSDI</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>1999999554</v>
+      </c>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260929000507</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K160"/>
+  <dimension ref="A1:K167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5803,10 +5803,6 @@
       <c r="F159" t="n">
         <v>1100002810</v>
       </c>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260929000646</t>
@@ -5840,13 +5836,276 @@
       <c r="F160" t="n">
         <v>1999999554</v>
       </c>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260929000507</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>엑스플러스</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>2999999520</v>
+      </c>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260930000823</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>한화투자증권</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>유상증자(보통+기타)</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>500000000000</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>한화투자증권(4,800,000주)</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260930000770</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>태영건설</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>23449995030</v>
+      </c>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260930000687</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>파인테크닉스</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>999997800</v>
+      </c>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260930000471</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>진시스템</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>5800000000</v>
+      </c>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260930000411</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>삼영이엔씨</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260930000221</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>삼영이엔씨</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>6353782500</v>
+      </c>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260930000197</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K167"/>
+  <dimension ref="A1:K170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5869,10 +5869,6 @@
       <c r="F161" t="n">
         <v>2999999520</v>
       </c>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr"/>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260930000823</t>
@@ -5911,9 +5907,6 @@
           <t>한화투자증권(4,800,000주)</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr"/>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260930000770</t>
@@ -5947,10 +5940,6 @@
       <c r="F163" t="n">
         <v>23449995030</v>
       </c>
-      <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr"/>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260930000687</t>
@@ -5984,10 +5973,6 @@
       <c r="F164" t="n">
         <v>999997800</v>
       </c>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260930000471</t>
@@ -6021,14 +6006,11 @@
       <c r="F165" t="n">
         <v>5800000000</v>
       </c>
-      <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260930000411</t>
@@ -6062,10 +6044,6 @@
       <c r="F166" t="n">
         <v>10000000000</v>
       </c>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260930000221</t>
@@ -6099,13 +6077,120 @@
       <c r="F167" t="n">
         <v>6353782500</v>
       </c>
-      <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260930000197</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>엔시스</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>8000000000</v>
+      </c>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261001000515</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>다보링크</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>1728272000</v>
+      </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261001000364</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>청보</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260930000878</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K170"/>
+  <dimension ref="A1:K176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6110,10 +6110,6 @@
       <c r="F168" t="n">
         <v>8000000000</v>
       </c>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261001000515</t>
@@ -6147,10 +6143,6 @@
       <c r="F169" t="n">
         <v>1728272000</v>
       </c>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261001000364</t>
@@ -6184,13 +6176,235 @@
       <c r="F170" t="n">
         <v>1000000000</v>
       </c>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20260930000878</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>20261006</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>에코앤드림</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>35000000000</v>
+      </c>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261006000446</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>20261006</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>리튬포어스</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>1320524016</v>
+      </c>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261006000392</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>20261006</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>유상증자(기타주식)</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>49999918909</v>
+      </c>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261006000329</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>20261006</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>유상증자(기타주식)</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>49999762236</v>
+      </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261006000323</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>20261006</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>유상증자(기타주식)</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>49999918909</v>
+      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261006000321</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>20261006</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>유상증자(기타주식)</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>49999762236</v>
+      </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261006000310</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K176"/>
+  <dimension ref="A1:K181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6209,14 +6209,11 @@
       <c r="F171" t="n">
         <v>35000000000</v>
       </c>
-      <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261006000446</t>
@@ -6250,10 +6247,6 @@
       <c r="F172" t="n">
         <v>1320524016</v>
       </c>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261006000392</t>
@@ -6287,10 +6280,6 @@
       <c r="F173" t="n">
         <v>49999918909</v>
       </c>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261006000329</t>
@@ -6324,10 +6313,6 @@
       <c r="F174" t="n">
         <v>49999762236</v>
       </c>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261006000323</t>
@@ -6361,10 +6346,6 @@
       <c r="F175" t="n">
         <v>49999918909</v>
       </c>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261006000321</t>
@@ -6398,13 +6379,194 @@
       <c r="F176" t="n">
         <v>49999762236</v>
       </c>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261006000310</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>20261007</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>에피소드컴퍼니</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>13999991040</v>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261007000450</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>20261007</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>에피소드컴퍼니</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>1999998720</v>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261007000447</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>20261007</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>빛과전자</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261007000422</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>20261007</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>나노팀</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>20000000000</v>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261007000391</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>20261007</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>KG에코솔루션</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>EB</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>16254726432</v>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261007000250</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K181"/>
+  <dimension ref="A1:K182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6412,10 +6412,6 @@
       <c r="F177" t="n">
         <v>13999991040</v>
       </c>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261007000450</t>
@@ -6449,10 +6445,6 @@
       <c r="F178" t="n">
         <v>1999998720</v>
       </c>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261007000447</t>
@@ -6486,10 +6478,6 @@
       <c r="F179" t="n">
         <v>3000000000</v>
       </c>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr"/>
-      <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261007000422</t>
@@ -6523,10 +6511,6 @@
       <c r="F180" t="n">
         <v>20000000000</v>
       </c>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261007000391</t>
@@ -6560,13 +6544,46 @@
       <c r="F181" t="n">
         <v>16254726432</v>
       </c>
-      <c r="G181" t="inlineStr"/>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261007000250</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>티엑스알로보틱스</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>30000000000</v>
+      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261012000285</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K182"/>
+  <dimension ref="A1:K187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6577,13 +6577,195 @@
       <c r="F182" t="n">
         <v>30000000000</v>
       </c>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261012000285</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>BW</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>100000000000</v>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261013000372</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>두산퓨얼셀</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>300000000000</v>
+      </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261013000355</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>110000000000</v>
+      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261013000138</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>제일엠앤에스</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>15500000000</v>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261013000002</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>제일엠앤에스</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261012000514</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K187"/>
+  <dimension ref="A1:K193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6610,10 +6610,6 @@
       <c r="F183" t="n">
         <v>100000000000</v>
       </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261013000372</t>
@@ -6647,10 +6643,6 @@
       <c r="F184" t="n">
         <v>300000000000</v>
       </c>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261013000355</t>
@@ -6684,14 +6676,11 @@
       <c r="F185" t="n">
         <v>110000000000</v>
       </c>
-      <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261013000138</t>
@@ -6725,10 +6714,6 @@
       <c r="F186" t="n">
         <v>15500000000</v>
       </c>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261013000002</t>
@@ -6759,13 +6744,231 @@
           <t>유상증자(보통주식)</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261012000514</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>리메드</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261014000424</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>휴맥스</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>4999996680</v>
+      </c>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261014000405</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>엘에이티</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>코넥스</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>671681500</v>
+      </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261014000348</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>오션스바이오</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>코넥스</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>유상증자(기타주식)</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>899997000</v>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261014000342</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>대주전자재료</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>70000000000</v>
+      </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261014000146</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>하이퍼코퍼레이션</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>10999998855</v>
+      </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261014000001</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K193"/>
+  <dimension ref="A1:K198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6777,10 +6777,6 @@
       <c r="F188" t="n">
         <v>10000000000</v>
       </c>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261014000424</t>
@@ -6814,10 +6810,6 @@
       <c r="F189" t="n">
         <v>4999996680</v>
       </c>
-      <c r="G189" t="inlineStr"/>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261014000405</t>
@@ -6851,10 +6843,6 @@
       <c r="F190" t="n">
         <v>671681500</v>
       </c>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261014000348</t>
@@ -6888,10 +6876,6 @@
       <c r="F191" t="n">
         <v>899997000</v>
       </c>
-      <c r="G191" t="inlineStr"/>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261014000342</t>
@@ -6925,10 +6909,6 @@
       <c r="F192" t="n">
         <v>70000000000</v>
       </c>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261014000146</t>
@@ -6962,13 +6942,202 @@
       <c r="F193" t="n">
         <v>10999998855</v>
       </c>
-      <c r="G193" t="inlineStr"/>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261014000001</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>시지트로닉스</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>762480095</v>
+      </c>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261015000313</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>이오플로우</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>신종자본증권(3,333,333주)</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261015000232</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>KS인더스트리</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>4999999059</v>
+      </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261015000184</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>큐로홀딩스</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>8091912500</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>큐로홀딩스(7,600,024주)</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261015000163</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>테크트랜스</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>코넥스</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>913840271</v>
+      </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261014000461</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K198"/>
+  <dimension ref="A1:K200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6975,10 +6975,6 @@
       <c r="F194" t="n">
         <v>762480095</v>
       </c>
-      <c r="G194" t="inlineStr"/>
-      <c r="H194" t="inlineStr"/>
-      <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261015000313</t>
@@ -7017,9 +7013,6 @@
           <t>신종자본증권(3,333,333주)</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261015000232</t>
@@ -7053,10 +7046,6 @@
       <c r="F196" t="n">
         <v>4999999059</v>
       </c>
-      <c r="G196" t="inlineStr"/>
-      <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261015000184</t>
@@ -7095,9 +7084,6 @@
           <t>큐로홀딩스(7,600,024주)</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261015000163</t>
@@ -7131,13 +7117,83 @@
       <c r="F198" t="n">
         <v>913840271</v>
       </c>
-      <c r="G198" t="inlineStr"/>
-      <c r="H198" t="inlineStr"/>
-      <c r="I198" t="inlineStr"/>
-      <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261014000461</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>금호건설</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>50000000000</v>
+      </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261020000370</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>29000000000</v>
+      </c>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261020000332</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K200"/>
+  <dimension ref="A1:K208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7150,10 +7150,6 @@
       <c r="F199" t="n">
         <v>50000000000</v>
       </c>
-      <c r="G199" t="inlineStr"/>
-      <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261020000370</t>
@@ -7187,13 +7183,310 @@
       <c r="F200" t="n">
         <v>29000000000</v>
       </c>
-      <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261020000332</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>루멘스바이오스</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>18000000000</v>
+      </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261021000431</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>SKAI</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>22815000000</v>
+      </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261021000407</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>애드포러스</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>6000000000</v>
+      </c>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261021000401</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>에이루트</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>1699995492</v>
+      </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261021000326</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>알에프텍</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>5000000000</v>
+      </c>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261021000315</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>알에프텍</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261021000302</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>알에프텍</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>8999992440</v>
+      </c>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261021000276</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>한국유니온제약</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261021000091</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K208"/>
+  <dimension ref="A1:K216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7216,10 +7216,6 @@
       <c r="F201" t="n">
         <v>18000000000</v>
       </c>
-      <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr"/>
-      <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261021000431</t>
@@ -7253,10 +7249,6 @@
       <c r="F202" t="n">
         <v>22815000000</v>
       </c>
-      <c r="G202" t="inlineStr"/>
-      <c r="H202" t="inlineStr"/>
-      <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261021000407</t>
@@ -7290,10 +7282,6 @@
       <c r="F203" t="n">
         <v>6000000000</v>
       </c>
-      <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr"/>
-      <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261021000401</t>
@@ -7327,10 +7315,6 @@
       <c r="F204" t="n">
         <v>1699995492</v>
       </c>
-      <c r="G204" t="inlineStr"/>
-      <c r="H204" t="inlineStr"/>
-      <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261021000326</t>
@@ -7364,14 +7348,11 @@
       <c r="F205" t="n">
         <v>5000000000</v>
       </c>
-      <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261021000315</t>
@@ -7405,14 +7386,11 @@
       <c r="F206" t="n">
         <v>10000000000</v>
       </c>
-      <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261021000302</t>
@@ -7446,10 +7424,6 @@
       <c r="F207" t="n">
         <v>8999992440</v>
       </c>
-      <c r="G207" t="inlineStr"/>
-      <c r="H207" t="inlineStr"/>
-      <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261021000276</t>
@@ -7480,13 +7454,321 @@
           <t>유상증자(보통주식)</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr"/>
-      <c r="H208" t="inlineStr"/>
-      <c r="I208" t="inlineStr"/>
-      <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261021000091</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>대동</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>6000000000</v>
+      </c>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261022000505</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>교보증권</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>유상증자(기타주식)</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>199999938114</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>교보증권(113,962,961주)</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261022000492</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>교보증권</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>유상증자(기타주식)</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>99999955830</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>교보증권(113,962,961주)</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261022000488</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>엑스페릭스</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>1999997900</v>
+      </c>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261022000486</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>휴맥스</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>5000000000</v>
+      </c>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261022000365</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>에이팩트</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>29999995146</v>
+      </c>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261022000194</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>시큐레터</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>700002114</v>
+      </c>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261022000116</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>미래아이앤지</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>10000001000</v>
+      </c>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261022000100</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K216"/>
+  <dimension ref="A1:K219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7487,14 +7487,11 @@
       <c r="F209" t="n">
         <v>6000000000</v>
       </c>
-      <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr"/>
-      <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261022000505</t>
@@ -7533,9 +7530,6 @@
           <t>교보증권(113,962,961주)</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr"/>
-      <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261022000492</t>
@@ -7574,9 +7568,6 @@
           <t>교보증권(113,962,961주)</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr"/>
-      <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261022000488</t>
@@ -7610,10 +7601,6 @@
       <c r="F212" t="n">
         <v>1999997900</v>
       </c>
-      <c r="G212" t="inlineStr"/>
-      <c r="H212" t="inlineStr"/>
-      <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261022000486</t>
@@ -7647,14 +7634,11 @@
       <c r="F213" t="n">
         <v>5000000000</v>
       </c>
-      <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261022000365</t>
@@ -7688,10 +7672,6 @@
       <c r="F214" t="n">
         <v>29999995146</v>
       </c>
-      <c r="G214" t="inlineStr"/>
-      <c r="H214" t="inlineStr"/>
-      <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261022000194</t>
@@ -7725,10 +7705,6 @@
       <c r="F215" t="n">
         <v>700002114</v>
       </c>
-      <c r="G215" t="inlineStr"/>
-      <c r="H215" t="inlineStr"/>
-      <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261022000116</t>
@@ -7762,13 +7738,120 @@
       <c r="F216" t="n">
         <v>10000001000</v>
       </c>
-      <c r="G216" t="inlineStr"/>
-      <c r="H216" t="inlineStr"/>
-      <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261022000100</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>20261026</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>에이전트AI</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>7000000362</v>
+      </c>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261026000355</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>20261026</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>알티캐스트</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>1489998840</v>
+      </c>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261026000327</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>20261026</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>풍전약품</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261026000213</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K219"/>
+  <dimension ref="A1:K223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7771,10 +7771,6 @@
       <c r="F217" t="n">
         <v>7000000362</v>
       </c>
-      <c r="G217" t="inlineStr"/>
-      <c r="H217" t="inlineStr"/>
-      <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261026000355</t>
@@ -7808,10 +7804,6 @@
       <c r="F218" t="n">
         <v>1489998840</v>
       </c>
-      <c r="G218" t="inlineStr"/>
-      <c r="H218" t="inlineStr"/>
-      <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261026000327</t>
@@ -7845,13 +7837,161 @@
       <c r="F219" t="n">
         <v>3000000000</v>
       </c>
-      <c r="G219" t="inlineStr"/>
-      <c r="H219" t="inlineStr"/>
-      <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261026000213</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>20261027</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>비케이홀딩스</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>비케이홀딩스(711,743주)</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261027000379</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>20261027</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>핑거</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261027000338</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>20261027</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>SKAI</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>999999054</v>
+      </c>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261027000281</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>20261027</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>HD현대</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>EB</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>588667443000</v>
+      </c>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261027000277</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K223"/>
+  <dimension ref="A1:K224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7875,9 +7875,6 @@
           <t>비케이홀딩스(711,743주)</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr"/>
-      <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261027000379</t>
@@ -7911,10 +7908,6 @@
       <c r="F221" t="n">
         <v>10000000000</v>
       </c>
-      <c r="G221" t="inlineStr"/>
-      <c r="H221" t="inlineStr"/>
-      <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261027000338</t>
@@ -7948,10 +7941,6 @@
       <c r="F222" t="n">
         <v>999999054</v>
       </c>
-      <c r="G222" t="inlineStr"/>
-      <c r="H222" t="inlineStr"/>
-      <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261027000281</t>
@@ -7985,13 +7974,46 @@
       <c r="F223" t="n">
         <v>588667443000</v>
       </c>
-      <c r="G223" t="inlineStr"/>
-      <c r="H223" t="inlineStr"/>
-      <c r="I223" t="inlineStr"/>
-      <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261027000277</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>20261028</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>지엔코</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>2999999520</v>
+      </c>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261028000430</t>
         </is>
       </c>
     </row>

--- a/메자닌_발행사항_자동수집.xlsx
+++ b/메자닌_발행사항_자동수집.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K224"/>
+  <dimension ref="A1:K231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8007,13 +8007,272 @@
       <c r="F224" t="n">
         <v>2999999520</v>
       </c>
-      <c r="G224" t="inlineStr"/>
-      <c r="H224" t="inlineStr"/>
-      <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
           <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261028000430</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>20261029</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>쏘닉스</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>10000000000</v>
+      </c>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261029000654</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>20261029</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>유티아이</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>1324299540</v>
+      </c>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261029000479</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>20261029</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>와이랩</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261029000503</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>20261029</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>다스코</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>BW</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>6000000000</v>
+      </c>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261029000401</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>20261029</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>태영건설</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>27147170820</v>
+      </c>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261029000415</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>20261029</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>에이엘티</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>12200000000</v>
+      </c>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261029000290</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>20261029</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>씨아이테크</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>유상증자(보통주식)</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>2000004000</v>
+      </c>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>https://dart.fss.or.kr/dsaf001/main.do?rcpNo=20261029000183</t>
         </is>
       </c>
     </row>
